--- a/artfynd/A 3025-2026 artfynd.xlsx
+++ b/artfynd/A 3025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118836173</v>
+        <v>118834828</v>
       </c>
       <c r="B2" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +705,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532168</v>
+        <v>532071</v>
       </c>
       <c r="R2" t="n">
-        <v>6547203</v>
+        <v>6547043</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,15 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118834835</v>
+        <v>118834829</v>
       </c>
       <c r="B3" t="n">
-        <v>57298</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,27 +830,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vallbytorpakärren, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532155</v>
+        <v>531999</v>
       </c>
       <c r="R3" t="n">
-        <v>6547113</v>
+        <v>6547020</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -882,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +909,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Angelia Ellvin</t>
+          <t>Sara Poppelaars</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -928,32 +920,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118834114</v>
+        <v>118834835</v>
       </c>
       <c r="B4" t="n">
-        <v>57833</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,29 +950,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vallbytorpakärren, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532141</v>
+        <v>532155</v>
       </c>
       <c r="R4" t="n">
-        <v>6547185</v>
+        <v>6547113</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,15 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118833447</v>
+        <v>118834836</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,21 +1054,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1098,12 +1078,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1112,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532182</v>
+        <v>532035</v>
       </c>
       <c r="R5" t="n">
-        <v>6547165</v>
+        <v>6547013</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1147,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1157,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,32 +1163,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118834828</v>
+        <v>118834789</v>
       </c>
       <c r="B6" t="n">
-        <v>57298</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>100065</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1226,14 +1196,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1242,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532071</v>
+        <v>532013</v>
       </c>
       <c r="R6" t="n">
-        <v>6547043</v>
+        <v>6546999</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1272,22 +1237,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1272,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1318,15 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118834836</v>
+        <v>118834114</v>
       </c>
       <c r="B7" t="n">
-        <v>57298</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1334,16 +1294,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>102990</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1358,7 +1318,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1367,10 +1332,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532035</v>
+        <v>532141</v>
       </c>
       <c r="R7" t="n">
-        <v>6547013</v>
+        <v>6547185</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1402,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1412,7 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1443,15 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118833394</v>
+        <v>118834115</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,21 +1419,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1481,6 +1441,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1492,13 +1457,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532126</v>
+        <v>532193</v>
       </c>
       <c r="R8" t="n">
-        <v>6547087</v>
+        <v>6547235</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1522,22 +1487,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1557,7 +1522,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ola Erlandsson</t>
+          <t>Angelia Ellvin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1568,15 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118836206</v>
+        <v>118833394</v>
       </c>
       <c r="B9" t="n">
-        <v>57773</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,21 +1544,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1606,11 +1566,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -1622,10 +1577,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532265</v>
+        <v>532126</v>
       </c>
       <c r="R9" t="n">
-        <v>6547206</v>
+        <v>6547087</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1652,22 +1607,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,10 +1642,1125 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
+          <t>Ola Erlandsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>118833447</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>532182</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6547165</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Angelia Ellvin</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118833448</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>532202</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6547105</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118836205</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>532281</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6547214</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118836206</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>532265</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6547206</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118836234</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>532049</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6546965</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>05:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>05:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Engla Grönvall</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118836252</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>532154</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6547106</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118836253</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>531998</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6547029</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118836173</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>532168</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6547203</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Alight - Brevens bruk</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118835778</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vallbytorpakärren, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>532033</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6547061</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Asker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Angelia Ellvin</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Alight - Brevens bruk</t>
         </is>

--- a/artfynd/A 3025-2026 artfynd.xlsx
+++ b/artfynd/A 3025-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834828</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834829</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834836</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,6 +1177,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,6 +1307,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118833394</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836234</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1652,6 +1692,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836253</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1777,6 +1822,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118835778</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1900,6 +1950,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834835</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2025,6 +2080,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118834115</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2150,6 +2210,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118833447</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2270,6 +2335,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118833448</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2395,6 +2465,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836205</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2520,6 +2595,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836206</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2645,6 +2725,11 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836252</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2765,8 +2850,32 @@
           <t>Alight - Brevens bruk</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118836173</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>